--- a/data/trans_dic/P2C_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,55; 34,51</t>
+          <t>27,69; 34,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,32; 50,51</t>
+          <t>42,94; 50,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,29; 37,66</t>
+          <t>30,23; 37,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,83; 16,28</t>
+          <t>10,76; 16,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,43; 41,79</t>
+          <t>34,47; 41,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,93; 55,83</t>
+          <t>47,65; 55,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,04; 40,58</t>
+          <t>33,46; 40,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 18,79</t>
+          <t>12,78; 18,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,92; 37,09</t>
+          <t>31,94; 37,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,98; 52,5</t>
+          <t>46,95; 52,14</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,86; 38,33</t>
+          <t>32,68; 37,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,42; 16,5</t>
+          <t>12,43; 16,54</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,7; 34,17</t>
+          <t>27,93; 33,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,16; 51,68</t>
+          <t>45,2; 51,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,25; 37,03</t>
+          <t>30,98; 37,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,04; 16,24</t>
+          <t>6,02; 16,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,78; 38,22</t>
+          <t>31,76; 37,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,66; 58,63</t>
+          <t>52,36; 58,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,1; 46,29</t>
+          <t>40,18; 46,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,54; 24,94</t>
+          <t>20,53; 25,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,67; 34,89</t>
+          <t>30,55; 34,91</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,78; 54,18</t>
+          <t>49,73; 54,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,45; 40,83</t>
+          <t>36,31; 40,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 19,5</t>
+          <t>11,31; 19,49</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,06; 32,32</t>
+          <t>24,74; 32,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,79; 48,71</t>
+          <t>40,53; 48,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,73; 34,86</t>
+          <t>27,65; 34,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,87; 14,26</t>
+          <t>8,68; 14,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,98; 36,96</t>
+          <t>29,74; 36,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,23; 56,85</t>
+          <t>49,52; 57,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,48; 43,53</t>
+          <t>36,59; 43,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,05; 62,85</t>
+          <t>14,95; 66,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,59; 33,73</t>
+          <t>28,68; 33,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,09; 51,5</t>
+          <t>46,09; 51,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,2; 38,06</t>
+          <t>33,2; 38,14</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,25; 48,9</t>
+          <t>13,15; 48,68</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,1; 29,57</t>
+          <t>24,11; 29,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,2; 42,5</t>
+          <t>36,33; 42,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,11; 30,11</t>
+          <t>24,0; 29,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,19; 13,6</t>
+          <t>9,45; 13,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,58; 35,55</t>
+          <t>29,87; 35,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,48; 49,75</t>
+          <t>43,33; 49,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,13; 37,39</t>
+          <t>31,41; 37,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,99; 14,56</t>
+          <t>9,85; 14,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,68; 31,93</t>
+          <t>27,62; 31,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,88; 45,32</t>
+          <t>40,7; 45,55</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,67; 32,83</t>
+          <t>28,67; 32,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 13,53</t>
+          <t>10,4; 13,47</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,44; 30,83</t>
+          <t>27,54; 30,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,15; 46,51</t>
+          <t>43,05; 46,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,7; 32,72</t>
+          <t>29,72; 32,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,61; 13,38</t>
+          <t>9,34; 13,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,87; 36,05</t>
+          <t>32,93; 36,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,93; 53,43</t>
+          <t>49,94; 53,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,04; 40,48</t>
+          <t>37,14; 40,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,39; 36,32</t>
+          <t>16,32; 35,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,68; 32,91</t>
+          <t>30,84; 33,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46,82; 49,42</t>
+          <t>47,12; 49,56</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,91; 36,26</t>
+          <t>33,92; 36,24</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,87; 26,0</t>
+          <t>13,97; 23,9</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados</t>
+          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>191187; 239538</t>
+          <t>192187; 240614</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>304724; 355353</t>
+          <t>302075; 356761</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>204368; 254109</t>
+          <t>204026; 255131</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68821; 103440</t>
+          <t>68395; 102039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>237023; 287657</t>
+          <t>237303; 286885</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>334126; 389167</t>
+          <t>332117; 388641</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>222286; 273020</t>
+          <t>225147; 273264</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>90592; 136278</t>
+          <t>92714; 134633</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>441287; 512707</t>
+          <t>441490; 511954</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>657916; 735263</t>
+          <t>657482; 730272</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>442775; 516508</t>
+          <t>440353; 510169</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>168960; 224581</t>
+          <t>169204; 225073</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>266396; 328633</t>
+          <t>268618; 324301</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>459723; 526082</t>
+          <t>460161; 523635</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>319556; 378636</t>
+          <t>316785; 379648</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72096; 193774</t>
+          <t>71828; 192059</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>307787; 370139</t>
+          <t>307578; 367824</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>543506; 605210</t>
+          <t>540486; 604273</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>418193; 482772</t>
+          <t>419003; 483163</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>196867; 239066</t>
+          <t>196851; 240376</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>592004; 673383</t>
+          <t>589580; 673921</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1020606; 1110662</t>
+          <t>1019623; 1110375</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>752799; 843225</t>
+          <t>750028; 842687</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>236442; 419626</t>
+          <t>243374; 419240</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>170030; 219308</t>
+          <t>167854; 219121</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>309000; 369067</t>
+          <t>307038; 365298</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>210654; 264744</t>
+          <t>210004; 262767</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62522; 100517</t>
+          <t>61178; 99981</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>205016; 252728</t>
+          <t>203375; 252239</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>382586; 441786</t>
+          <t>384843; 443842</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>286348; 341743</t>
+          <t>287229; 340617</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>140460; 586643</t>
+          <t>139557; 625264</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>389522; 459543</t>
+          <t>390753; 460137</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>707422; 790395</t>
+          <t>707368; 793900</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>512736; 587789</t>
+          <t>512830; 589078</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>217056; 801012</t>
+          <t>215445; 797415</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>227032; 278633</t>
+          <t>227202; 280920</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>343068; 402836</t>
+          <t>344320; 404429</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>226076; 282261</t>
+          <t>225033; 280594</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85163; 126055</t>
+          <t>87560; 128108</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>307198; 369182</t>
+          <t>310265; 369336</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>457412; 523310</t>
+          <t>455821; 519125</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>324913; 390288</t>
+          <t>327801; 392616</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>109414; 159446</t>
+          <t>107866; 159893</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>548297; 632577</t>
+          <t>547132; 631088</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>817465; 906268</t>
+          <t>813937; 910770</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>568087; 650513</t>
+          <t>568053; 652741</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>212000; 273600</t>
+          <t>210297; 272427</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>899229; 1010203</t>
+          <t>902370; 1007998</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1478659; 1593946</t>
+          <t>1475400; 1592229</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1007995; 1110714</t>
+          <t>1008815; 1117687</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>332435; 462865</t>
+          <t>323099; 461845</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1110807; 1218215</t>
+          <t>1112673; 1224850</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1776561; 1901319</t>
+          <t>1777181; 1901415</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1312864; 1434726</t>
+          <t>1316269; 1436404</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>608615; 1348448</t>
+          <t>605896; 1323806</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2042280; 2190236</t>
+          <t>2052399; 2205057</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3270192; 3452205</t>
+          <t>3291292; 3461983</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2353086; 2516177</t>
+          <t>2353450; 2514349</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>995109; 1864797</t>
+          <t>1002271; 1713776</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,69; 34,67</t>
+          <t>27,08; 34,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,94; 50,71</t>
+          <t>43,23; 50,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,23; 37,81</t>
+          <t>30,51; 37,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,76; 16,06</t>
+          <t>10,45; 16,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,47; 41,68</t>
+          <t>34,33; 41,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,65; 55,76</t>
+          <t>48,36; 56,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,46; 40,61</t>
+          <t>33,15; 40,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,78; 18,56</t>
+          <t>14,95; 19,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31,94; 37,03</t>
+          <t>31,92; 37,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46,95; 52,14</t>
+          <t>46,72; 52,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,68; 37,86</t>
+          <t>32,83; 38,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,43; 16,54</t>
+          <t>13,49; 16,97</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>19,77%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,93; 33,72</t>
+          <t>27,58; 33,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,2; 51,44</t>
+          <t>45,33; 51,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,98; 37,13</t>
+          <t>31,1; 37,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 16,1</t>
+          <t>14,29; 19,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,76; 37,98</t>
+          <t>31,5; 38,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,36; 58,54</t>
+          <t>52,23; 58,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,18; 46,33</t>
+          <t>40,2; 46,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,53; 25,07</t>
+          <t>20,52; 24,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,55; 34,91</t>
+          <t>30,66; 35,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49,73; 54,16</t>
+          <t>49,73; 54,34</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36,31; 40,8</t>
+          <t>36,45; 40,78</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,31; 19,49</t>
+          <t>18,03; 21,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>14,57%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>24,74; 32,29</t>
+          <t>24,93; 32,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40,53; 48,22</t>
+          <t>40,99; 48,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,65; 34,59</t>
+          <t>27,51; 34,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,68; 14,19</t>
+          <t>9,16; 14,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,74; 36,89</t>
+          <t>29,8; 36,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,52; 57,11</t>
+          <t>49,04; 56,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36,59; 43,39</t>
+          <t>36,5; 43,41</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,95; 66,99</t>
+          <t>15,14; 20,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28,68; 33,78</t>
+          <t>28,63; 33,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46,09; 51,73</t>
+          <t>46,47; 51,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>33,2; 38,14</t>
+          <t>33,09; 38,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,15; 48,68</t>
+          <t>12,69; 16,48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,11; 29,81</t>
+          <t>24,19; 29,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,33; 42,67</t>
+          <t>36,02; 42,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24,0; 29,93</t>
+          <t>24,08; 29,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,45; 13,82</t>
+          <t>10,15; 14,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,87; 35,56</t>
+          <t>29,63; 35,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,33; 49,35</t>
+          <t>43,17; 49,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,41; 37,61</t>
+          <t>31,64; 37,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,85; 14,6</t>
+          <t>12,73; 16,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,62; 31,86</t>
+          <t>27,93; 31,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,7; 45,55</t>
+          <t>40,59; 45,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28,67; 32,94</t>
+          <t>28,93; 33,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,4; 13,47</t>
+          <t>12,03; 14,79</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,54; 30,76</t>
+          <t>27,69; 30,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,05; 46,46</t>
+          <t>43,01; 46,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29,72; 32,93</t>
+          <t>29,68; 32,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,35</t>
+          <t>12,4; 14,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,93; 36,25</t>
+          <t>32,84; 36,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,94; 53,44</t>
+          <t>49,9; 53,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,14; 40,52</t>
+          <t>37,04; 40,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 35,66</t>
+          <t>16,95; 19,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,84; 33,13</t>
+          <t>30,74; 33,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47,12; 49,56</t>
+          <t>47,08; 49,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33,92; 36,24</t>
+          <t>33,89; 36,32</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,97; 23,9</t>
+          <t>15,09; 16,8</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83078</t>
+          <t>90349</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>116125</t>
+          <t>126115</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>199203</t>
+          <t>216464</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>192187; 240614</t>
+          <t>187932; 238129</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>302075; 356761</t>
+          <t>304092; 357430</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>204026; 255131</t>
+          <t>205889; 253412</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>68395; 102039</t>
+          <t>72196; 111454</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>237303; 286885</t>
+          <t>236345; 287566</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>332117; 388641</t>
+          <t>337103; 393348</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>225147; 273264</t>
+          <t>223041; 272767</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>92714; 134633</t>
+          <t>109741; 145150</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>441490; 511954</t>
+          <t>441286; 514275</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>657482; 730272</t>
+          <t>654271; 732833</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>440353; 510169</t>
+          <t>442454; 514786</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>169204; 225073</t>
+          <t>192195; 241865</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>144948</t>
+          <t>175476</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>217129</t>
+          <t>243790</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>362077</t>
+          <t>419266</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>268618; 324301</t>
+          <t>265309; 323060</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>460161; 523635</t>
+          <t>461470; 527434</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>316785; 379648</t>
+          <t>318025; 380714</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>71828; 192059</t>
+          <t>149871; 205984</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>307578; 367824</t>
+          <t>305076; 369552</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>540486; 604273</t>
+          <t>539059; 608517</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>419003; 483163</t>
+          <t>419214; 484789</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>196851; 240376</t>
+          <t>219830; 267473</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>589580; 673921</t>
+          <t>591832; 676860</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1019623; 1110375</t>
+          <t>1019443; 1113971</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>750028; 842687</t>
+          <t>752795; 842194</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>243374; 419240</t>
+          <t>382375; 453888</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79720</t>
+          <t>93059</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>321229</t>
+          <t>142353</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>400949</t>
+          <t>235412</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>167854; 219121</t>
+          <t>169121; 217121</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>307038; 365298</t>
+          <t>310547; 368769</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>210004; 262767</t>
+          <t>208954; 263065</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>61178; 99981</t>
+          <t>73524; 117246</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>203375; 252239</t>
+          <t>203755; 252026</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>384843; 443842</t>
+          <t>381095; 439482</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>287229; 340617</t>
+          <t>286499; 340808</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>139557; 625264</t>
+          <t>122983; 164762</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>390753; 460137</t>
+          <t>390047; 459982</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>707368; 793900</t>
+          <t>713284; 792383</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>512830; 589078</t>
+          <t>511043; 587955</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>215445; 797415</t>
+          <t>204942; 266193</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>105188</t>
+          <t>119991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>138808</t>
+          <t>161496</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>243996</t>
+          <t>281487</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>227202; 280920</t>
+          <t>227896; 281143</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>344320; 404429</t>
+          <t>341386; 402619</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>225033; 280594</t>
+          <t>225727; 279644</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>87560; 128108</t>
+          <t>100446; 141931</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>310265; 369336</t>
+          <t>307704; 368110</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>455821; 519125</t>
+          <t>454055; 520492</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>327801; 392616</t>
+          <t>330259; 394486</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>107866; 159893</t>
+          <t>142402; 183689</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>547132; 631088</t>
+          <t>553315; 631688</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>813937; 910770</t>
+          <t>811647; 905086</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>568053; 652741</t>
+          <t>573145; 655539</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>210297; 272427</t>
+          <t>253738; 311846</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>412934</t>
+          <t>478875</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>793292</t>
+          <t>673754</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1206225</t>
+          <t>1152629</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>902370; 1007998</t>
+          <t>907289; 1008885</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1475400; 1592229</t>
+          <t>1473734; 1595276</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1008815; 1117687</t>
+          <t>1007320; 1112032</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>323099; 461845</t>
+          <t>438065; 523629</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1112673; 1224850</t>
+          <t>1109829; 1221313</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1777181; 1901415</t>
+          <t>1775443; 1895160</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1316269; 1436404</t>
+          <t>1312919; 1430779</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>605896; 1323806</t>
+          <t>633462; 716404</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2052399; 2205057</t>
+          <t>2046214; 2200666</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3291292; 3461983</t>
+          <t>3288658; 3459538</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2353450; 2514349</t>
+          <t>2351851; 2520436</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1002271; 1713776</t>
+          <t>1096644; 1221522</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2C_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P2C_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son no remunerados (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
